--- a/artifacts/api-server/assets/test-case-template.xlsx
+++ b/artifacts/api-server/assets/test-case-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/syamilabdulsamat/Desktop/QAPulse/QAPulse/artifacts/api-server/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE2C928-4509-6042-A696-46448DD8CE08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3416D63-D079-604D-8789-0E0A467B1C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4420" yWindow="880" windowWidth="31580" windowHeight="21120" tabRatio="713" activeTab="1" xr2:uid="{01A690A9-14C5-40FC-A7C5-3CCF81F623E0}"/>
+    <workbookView xWindow="4420" yWindow="880" windowWidth="31580" windowHeight="21120" tabRatio="713" xr2:uid="{01A690A9-14C5-40FC-A7C5-3CCF81F623E0}"/>
   </bookViews>
   <sheets>
     <sheet name="Doc Info" sheetId="5" r:id="rId1"/>
@@ -307,7 +307,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="85">
   <si>
     <t>Review</t>
   </si>
@@ -352,12 +352,6 @@
   </si>
   <si>
     <t>Syamil</t>
-  </si>
-  <si>
-    <t>Raimi</t>
-  </si>
-  <si>
-    <t>Final Test Cases</t>
   </si>
   <si>
     <t>Case ID</t>
@@ -1731,6 +1725,24 @@
     <xf numFmtId="0" fontId="23" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1761,24 +1773,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="41" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3505,14 +3499,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="125" t="s">
+      <c r="B1" s="131" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="128"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="134"/>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B2" s="41"/>
@@ -3520,17 +3514,17 @@
       <c r="D2" s="106"/>
       <c r="E2" s="41"/>
       <c r="F2" s="41"/>
-      <c r="G2" s="129"/>
+      <c r="G2" s="135"/>
     </row>
     <row r="3" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="125" t="s">
+      <c r="B3" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="126"/>
-      <c r="D3" s="126"/>
-      <c r="E3" s="126"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="129"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="132"/>
+      <c r="E3" s="132"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="135"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="41"/>
@@ -3543,10 +3537,10 @@
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B5" s="130" t="s">
+      <c r="B5" s="136" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="131"/>
+      <c r="C5" s="137"/>
       <c r="D5" s="111" t="s">
         <v>4</v>
       </c>
@@ -3557,20 +3551,20 @@
     <row r="6" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B6" s="41"/>
       <c r="C6" s="41"/>
-      <c r="D6" s="132"/>
-      <c r="E6" s="132"/>
-      <c r="F6" s="133"/>
+      <c r="D6" s="138"/>
+      <c r="E6" s="138"/>
+      <c r="F6" s="139"/>
       <c r="G6" s="115"/>
     </row>
     <row r="7" spans="2:7" ht="18" x14ac:dyDescent="0.2">
-      <c r="B7" s="121" t="s">
+      <c r="B7" s="127" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="122"/>
-      <c r="D7" s="123"/>
-      <c r="E7" s="123"/>
-      <c r="F7" s="123"/>
-      <c r="G7" s="124"/>
+      <c r="C7" s="128"/>
+      <c r="D7" s="129"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="129"/>
+      <c r="G7" s="130"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="43" t="s">
@@ -3616,21 +3610,11 @@
       <c r="B10" s="57">
         <v>2</v>
       </c>
-      <c r="C10" s="72">
-        <v>45803</v>
-      </c>
-      <c r="D10" s="105" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="42" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="72">
-        <v>45803</v>
-      </c>
+      <c r="C10" s="72"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="72"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B11" s="58">
@@ -3698,90 +3682,90 @@
   <sheetData>
     <row r="1" spans="2:16" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:16" ht="26" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="134" t="s">
+      <c r="B2" s="121" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="122"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="122"/>
+      <c r="F2" s="122"/>
+      <c r="G2" s="122"/>
+      <c r="H2" s="122"/>
+      <c r="I2" s="122"/>
+      <c r="J2" s="122"/>
+      <c r="K2" s="122"/>
+      <c r="L2" s="122"/>
+      <c r="M2" s="122"/>
+      <c r="N2" s="122"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="123"/>
+    </row>
+    <row r="3" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="124" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="125"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="125" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="135"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="135"/>
-      <c r="N2" s="135"/>
-      <c r="O2" s="135"/>
-      <c r="P2" s="136"/>
-    </row>
-    <row r="3" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="137" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="138"/>
-      <c r="D3" s="138"/>
-      <c r="E3" s="138"/>
-      <c r="F3" s="138"/>
-      <c r="G3" s="138"/>
-      <c r="H3" s="138"/>
-      <c r="I3" s="138"/>
-      <c r="J3" s="138"/>
-      <c r="K3" s="138"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="138" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="138"/>
-      <c r="O3" s="138"/>
-      <c r="P3" s="139"/>
+      <c r="N3" s="125"/>
+      <c r="O3" s="125"/>
+      <c r="P3" s="126"/>
     </row>
     <row r="4" spans="2:16" ht="71" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="46" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="F4" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="47" t="s">
+      <c r="G4" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="47" t="s">
+      <c r="H4" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="47" t="s">
+      <c r="I4" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="47" t="s">
+      <c r="J4" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="47" t="s">
+      <c r="K4" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="47" t="s">
+      <c r="L4" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="47" t="s">
+      <c r="M4" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="L4" s="48" t="s">
+      <c r="N4" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="M4" s="46" t="s">
+      <c r="O4" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="N4" s="47" t="s">
+      <c r="P4" s="48" t="s">
         <v>41</v>
-      </c>
-      <c r="O4" s="47" t="s">
-        <v>42</v>
-      </c>
-      <c r="P4" s="48" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.2">
@@ -3789,7 +3773,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D5" s="83">
         <v>1</v>
@@ -3799,25 +3783,25 @@
         <v>14</v>
       </c>
       <c r="G5" s="65" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I5" s="65">
         <v>28</v>
       </c>
       <c r="J5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="M5" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="N5" s="81">
         <v>45803</v>
@@ -3905,7 +3889,7 @@
       <c r="H10" s="3"/>
       <c r="I10" s="65"/>
       <c r="J10" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="3"/>
@@ -3924,7 +3908,7 @@
       <c r="H11" s="3"/>
       <c r="I11" s="65"/>
       <c r="J11" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="3"/>
@@ -4080,43 +4064,43 @@
   <sheetData>
     <row r="1" spans="1:13" ht="32.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="118" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="118" t="s">
+      <c r="E1" s="118" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="118" t="s">
+      <c r="F1" s="118" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="118" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="119" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" s="118" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="118" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="118" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1" s="120" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="118" t="s">
         <v>53</v>
-      </c>
-      <c r="D1" s="118" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="118" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="118" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="118" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" s="119" t="s">
-        <v>54</v>
-      </c>
-      <c r="I1" s="118" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="118" t="s">
-        <v>24</v>
-      </c>
-      <c r="K1" s="118" t="s">
-        <v>25</v>
-      </c>
-      <c r="L1" s="120" t="s">
-        <v>26</v>
-      </c>
-      <c r="M1" s="118" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -4141,24 +4125,24 @@
   <sheetData>
     <row r="1" spans="2:7" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:7" ht="26" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="134" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="136"/>
+      <c r="B2" s="121" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="122"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="122"/>
+      <c r="F2" s="122"/>
+      <c r="G2" s="123"/>
     </row>
     <row r="3" spans="2:7" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="140" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C3" s="140"/>
       <c r="D3" s="140"/>
       <c r="E3" s="140"/>
       <c r="F3" s="140" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G3" s="140"/>
     </row>
@@ -4167,19 +4151,19 @@
         <v>6</v>
       </c>
       <c r="C4" s="50" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" s="50" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E4" s="50" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F4" s="50" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G4" s="51" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
@@ -4187,16 +4171,16 @@
         <v>1</v>
       </c>
       <c r="C5" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="19" t="s">
-        <v>46</v>
-      </c>
       <c r="E5" s="94" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F5" s="93" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G5" s="20"/>
     </row>
@@ -4959,7 +4943,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="23" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -4980,7 +4964,7 @@
       <c r="G2" s="95"/>
       <c r="H2" s="95"/>
       <c r="I2" s="95" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.2">
@@ -5018,7 +5002,7 @@
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B23" s="28" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C23" s="95"/>
       <c r="D23" s="95"/>
@@ -5049,7 +5033,7 @@
       <c r="B31" s="95"/>
       <c r="C31" s="95"/>
       <c r="D31" s="99" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E31" s="100">
         <v>0.8</v>
@@ -5063,28 +5047,28 @@
     </row>
     <row r="32" spans="2:11" ht="16" x14ac:dyDescent="0.2">
       <c r="B32" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="C32" s="31" t="s">
+      <c r="E32" s="30" t="s">
         <v>65</v>
-      </c>
-      <c r="D32" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="E32" s="30" t="s">
-        <v>67</v>
       </c>
       <c r="F32" s="95"/>
       <c r="G32" s="95"/>
       <c r="H32" s="95"/>
       <c r="I32" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="J32" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="K32" s="33" t="s">
         <v>68</v>
-      </c>
-      <c r="J32" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="K32" s="33" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.15">
@@ -5093,7 +5077,7 @@
         <v>1</v>
       </c>
       <c r="C33" s="102" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D33" s="103">
         <v>50</v>
@@ -5124,7 +5108,7 @@
         <v>2</v>
       </c>
       <c r="C34" s="102" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D34" s="103">
         <v>30</v>
@@ -5155,7 +5139,7 @@
         <v>3</v>
       </c>
       <c r="C35" s="102" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D35" s="103">
         <v>15</v>
@@ -5186,7 +5170,7 @@
         <v>4</v>
       </c>
       <c r="C36" s="102" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D36" s="103">
         <v>5</v>
@@ -5217,7 +5201,7 @@
         <v>5</v>
       </c>
       <c r="C37" s="102" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D37" s="103">
         <v>3</v>
@@ -5248,7 +5232,7 @@
         <v>6</v>
       </c>
       <c r="C38" s="102" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D38" s="103">
         <v>2</v>
@@ -5279,7 +5263,7 @@
         <v>7</v>
       </c>
       <c r="C39" s="102" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D39" s="103">
         <v>1</v>
@@ -5310,7 +5294,7 @@
         <v>8</v>
       </c>
       <c r="C40" s="102" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D40" s="103">
         <v>1</v>
@@ -5341,7 +5325,7 @@
         <v>9</v>
       </c>
       <c r="C41" s="102" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D41" s="103">
         <v>1</v>
@@ -5530,7 +5514,7 @@
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B48" s="37" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C48" s="22"/>
       <c r="D48" s="22"/>
@@ -5571,7 +5555,7 @@
     <row r="1" spans="2:7" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:7" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="141" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C2" s="142"/>
       <c r="D2" s="142"/>
@@ -5584,19 +5568,19 @@
         <v>6</v>
       </c>
       <c r="C3" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="E3" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="D3" s="53" t="s">
+      <c r="F3" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="G3" s="54" t="s">
         <v>84</v>
-      </c>
-      <c r="F3" s="53" t="s">
-        <v>85</v>
-      </c>
-      <c r="G3" s="54" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
@@ -5672,6 +5656,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="14bdffc1-a38a-4965-b8c7-6b995394fa38">
@@ -5687,15 +5680,6 @@
     <TaxCatchAll xmlns="14bdffc1-a38a-4965-b8c7-6b995394fa38" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5948,20 +5932,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{887577A6-6A39-4FD8-B789-F26250D68B34}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C751A3DA-DA6E-456D-B998-BFDFBC6A10B1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="14bdffc1-a38a-4965-b8c7-6b995394fa38"/>
     <ds:schemaRef ds:uri="fa6523cc-f9d2-4d22-b899-9712b14156b8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{887577A6-6A39-4FD8-B789-F26250D68B34}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/artifacts/api-server/assets/test-case-template.xlsx
+++ b/artifacts/api-server/assets/test-case-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/syamilabdulsamat/Desktop/QAPulse/QAPulse/artifacts/api-server/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3416D63-D079-604D-8789-0E0A467B1C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78030303-D649-014D-9A5C-8609B68F7EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4420" yWindow="880" windowWidth="31580" windowHeight="21120" tabRatio="713" xr2:uid="{01A690A9-14C5-40FC-A7C5-3CCF81F623E0}"/>
+    <workbookView xWindow="4420" yWindow="880" windowWidth="31580" windowHeight="21120" tabRatio="713" activeTab="3" xr2:uid="{01A690A9-14C5-40FC-A7C5-3CCF81F623E0}"/>
   </bookViews>
   <sheets>
     <sheet name="Doc Info" sheetId="5" r:id="rId1"/>
@@ -236,7 +236,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -245,12 +245,21 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Mention as number "1st, 2nd or 3rd" review cycle, depending on the number of times document OR code/module was reviewed</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Mention as number "1st, 2nd or 3rd" review cycle, depending on the number of times document OR code/module was reviewed</t>
         </r>
       </text>
     </comment>
@@ -579,7 +588,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="[$-409]d\-mmm;@"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -742,6 +751,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -793,7 +815,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="42">
+  <borders count="47">
     <border>
       <left/>
       <right/>
@@ -1185,51 +1207,6 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -1322,6 +1299,110 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1340,7 +1421,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1495,24 +1576,6 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1552,14 +1615,6 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1703,44 +1758,29 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="36" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="38" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="23" fillId="8" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="23" fillId="8" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1768,11 +1808,29 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="35" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="38" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="41" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1785,6 +1843,63 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -3492,79 +3607,79 @@
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="6" customWidth="1"/>
     <col min="3" max="3" width="12.6640625" customWidth="1"/>
-    <col min="4" max="4" width="16.33203125" style="107" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" style="99" customWidth="1"/>
     <col min="5" max="5" width="53.6640625" customWidth="1"/>
     <col min="6" max="6" width="16.33203125" customWidth="1"/>
     <col min="7" max="7" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="131" t="s">
+      <c r="B1" s="118" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="134"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="121"/>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B2" s="41"/>
       <c r="C2" s="41"/>
-      <c r="D2" s="106"/>
+      <c r="D2" s="98"/>
       <c r="E2" s="41"/>
       <c r="F2" s="41"/>
-      <c r="G2" s="135"/>
+      <c r="G2" s="122"/>
     </row>
     <row r="3" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="131" t="s">
+      <c r="B3" s="118" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="132"/>
-      <c r="D3" s="132"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="135"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="120"/>
+      <c r="G3" s="122"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="41"/>
       <c r="C4" s="41"/>
-      <c r="D4" s="106"/>
+      <c r="D4" s="98"/>
       <c r="E4" s="41"/>
       <c r="F4" s="41"/>
-      <c r="G4" s="113" t="s">
+      <c r="G4" s="105" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B5" s="136" t="s">
+      <c r="B5" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="137"/>
-      <c r="D5" s="111" t="s">
+      <c r="C5" s="124"/>
+      <c r="D5" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="112"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="114"/>
+      <c r="E5" s="104"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="106"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B6" s="41"/>
       <c r="C6" s="41"/>
-      <c r="D6" s="138"/>
-      <c r="E6" s="138"/>
-      <c r="F6" s="139"/>
-      <c r="G6" s="115"/>
+      <c r="D6" s="125"/>
+      <c r="E6" s="125"/>
+      <c r="F6" s="126"/>
+      <c r="G6" s="107"/>
     </row>
     <row r="7" spans="2:7" ht="18" x14ac:dyDescent="0.2">
-      <c r="B7" s="127" t="s">
+      <c r="B7" s="114" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="128"/>
-      <c r="D7" s="129"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="129"/>
-      <c r="G7" s="130"/>
+      <c r="C7" s="115"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="117"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="43" t="s">
@@ -3587,13 +3702,13 @@
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B9" s="56">
+      <c r="B9" s="50">
         <v>1</v>
       </c>
-      <c r="C9" s="71">
+      <c r="C9" s="63">
         <v>45799</v>
       </c>
-      <c r="D9" s="105" t="s">
+      <c r="D9" s="97" t="s">
         <v>12</v>
       </c>
       <c r="E9" s="42" t="s">
@@ -3602,49 +3717,49 @@
       <c r="F9" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="71">
+      <c r="G9" s="63">
         <v>45800</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B10" s="57">
+      <c r="B10" s="51">
         <v>2</v>
       </c>
-      <c r="C10" s="72"/>
-      <c r="D10" s="105"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="97"/>
       <c r="E10" s="42"/>
       <c r="F10" s="42"/>
-      <c r="G10" s="72"/>
+      <c r="G10" s="64"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B11" s="58">
+      <c r="B11" s="52">
         <v>3</v>
       </c>
-      <c r="C11" s="72"/>
-      <c r="D11" s="105"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="97"/>
       <c r="E11" s="42"/>
       <c r="F11" s="42"/>
-      <c r="G11" s="73"/>
+      <c r="G11" s="65"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B12" s="59">
+      <c r="B12" s="53">
         <v>4</v>
       </c>
-      <c r="C12" s="72"/>
-      <c r="D12" s="105"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="97"/>
       <c r="E12" s="42"/>
       <c r="F12" s="42"/>
-      <c r="G12" s="72"/>
+      <c r="G12" s="64"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B13" s="59">
+      <c r="B13" s="53">
         <v>5</v>
       </c>
-      <c r="C13" s="72"/>
-      <c r="D13" s="105"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="97"/>
       <c r="E13" s="42"/>
       <c r="F13" s="42"/>
-      <c r="G13" s="72"/>
+      <c r="G13" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -3682,44 +3797,44 @@
   <sheetData>
     <row r="1" spans="2:16" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:16" ht="26" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="127" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="122"/>
-      <c r="D2" s="122"/>
-      <c r="E2" s="122"/>
-      <c r="F2" s="122"/>
-      <c r="G2" s="122"/>
-      <c r="H2" s="122"/>
-      <c r="I2" s="122"/>
-      <c r="J2" s="122"/>
-      <c r="K2" s="122"/>
-      <c r="L2" s="122"/>
-      <c r="M2" s="122"/>
-      <c r="N2" s="122"/>
-      <c r="O2" s="122"/>
-      <c r="P2" s="123"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="128"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="128"/>
+      <c r="O2" s="128"/>
+      <c r="P2" s="129"/>
     </row>
     <row r="3" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="124" t="s">
+      <c r="B3" s="130" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="125"/>
-      <c r="D3" s="125"/>
-      <c r="E3" s="125"/>
-      <c r="F3" s="125"/>
-      <c r="G3" s="125"/>
-      <c r="H3" s="125"/>
-      <c r="I3" s="125"/>
-      <c r="J3" s="125"/>
-      <c r="K3" s="125"/>
+      <c r="C3" s="131"/>
+      <c r="D3" s="131"/>
+      <c r="E3" s="131"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="131"/>
+      <c r="H3" s="131"/>
+      <c r="I3" s="131"/>
+      <c r="J3" s="131"/>
+      <c r="K3" s="131"/>
       <c r="L3" s="45"/>
-      <c r="M3" s="125" t="s">
+      <c r="M3" s="131" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="125"/>
-      <c r="O3" s="125"/>
-      <c r="P3" s="126"/>
+      <c r="N3" s="131"/>
+      <c r="O3" s="131"/>
+      <c r="P3" s="132"/>
     </row>
     <row r="4" spans="2:16" ht="71" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="46" t="s">
@@ -3769,26 +3884,26 @@
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B5" s="62">
+      <c r="B5" s="56">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="83">
+      <c r="D5" s="75">
         <v>1</v>
       </c>
-      <c r="E5" s="74"/>
+      <c r="E5" s="66"/>
       <c r="F5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="65" t="s">
+      <c r="G5" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I5" s="65">
+      <c r="I5" s="59">
         <v>28</v>
       </c>
       <c r="J5" s="4" t="s">
@@ -3803,220 +3918,220 @@
       <c r="M5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="N5" s="81">
+      <c r="N5" s="73">
         <v>45803</v>
       </c>
-      <c r="O5" s="81">
+      <c r="O5" s="73">
         <v>45803</v>
       </c>
       <c r="P5" s="11"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B6" s="61"/>
+      <c r="B6" s="55"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="74"/>
+      <c r="D6" s="75"/>
+      <c r="E6" s="66"/>
       <c r="F6" s="3"/>
-      <c r="G6" s="65"/>
+      <c r="G6" s="59"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="65"/>
+      <c r="I6" s="59"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
-      <c r="N6" s="81"/>
-      <c r="O6" s="81"/>
+      <c r="N6" s="73"/>
+      <c r="O6" s="73"/>
       <c r="P6" s="11"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B7" s="61"/>
+      <c r="B7" s="55"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="74"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="66"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="65"/>
+      <c r="G7" s="59"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="65"/>
+      <c r="I7" s="59"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="81"/>
-      <c r="O7" s="81"/>
+      <c r="N7" s="73"/>
+      <c r="O7" s="73"/>
       <c r="P7" s="11"/>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B8" s="61"/>
+      <c r="B8" s="55"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="83"/>
-      <c r="E8" s="74"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="66"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="65"/>
+      <c r="G8" s="59"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="65"/>
+      <c r="I8" s="59"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="81"/>
-      <c r="O8" s="81"/>
+      <c r="N8" s="73"/>
+      <c r="O8" s="73"/>
       <c r="P8" s="11"/>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B9" s="61"/>
+      <c r="B9" s="55"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="83"/>
-      <c r="E9" s="74"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="66"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="65"/>
+      <c r="G9" s="59"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="65"/>
+      <c r="I9" s="59"/>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="81"/>
-      <c r="O9" s="81"/>
+      <c r="N9" s="73"/>
+      <c r="O9" s="73"/>
       <c r="P9" s="11"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B10" s="61"/>
+      <c r="B10" s="55"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="83"/>
-      <c r="E10" s="74"/>
+      <c r="D10" s="75"/>
+      <c r="E10" s="66"/>
       <c r="F10" s="3"/>
-      <c r="G10" s="65"/>
+      <c r="G10" s="59"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="65"/>
+      <c r="I10" s="59"/>
       <c r="J10" s="4" t="s">
         <v>49</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
-      <c r="N10" s="81"/>
-      <c r="O10" s="81"/>
+      <c r="N10" s="73"/>
+      <c r="O10" s="73"/>
       <c r="P10" s="11"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B11" s="61"/>
+      <c r="B11" s="55"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="83"/>
-      <c r="E11" s="74"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="66"/>
       <c r="F11" s="3"/>
-      <c r="G11" s="65"/>
+      <c r="G11" s="59"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="65"/>
+      <c r="I11" s="59"/>
       <c r="J11" s="4" t="s">
         <v>50</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-      <c r="N11" s="81"/>
-      <c r="O11" s="81"/>
+      <c r="N11" s="73"/>
+      <c r="O11" s="73"/>
       <c r="P11" s="11"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B12" s="61"/>
+      <c r="B12" s="55"/>
       <c r="C12" s="5"/>
-      <c r="D12" s="84"/>
-      <c r="E12" s="75"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="67"/>
       <c r="F12" s="6"/>
-      <c r="G12" s="78"/>
+      <c r="G12" s="70"/>
       <c r="H12" s="6"/>
-      <c r="I12" s="78"/>
+      <c r="I12" s="70"/>
       <c r="J12" s="7"/>
       <c r="K12" s="4"/>
       <c r="L12" s="6"/>
       <c r="M12" s="3"/>
-      <c r="N12" s="81"/>
-      <c r="O12" s="81"/>
+      <c r="N12" s="73"/>
+      <c r="O12" s="73"/>
       <c r="P12" s="11"/>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B13" s="61"/>
+      <c r="B13" s="55"/>
       <c r="C13" s="8"/>
-      <c r="D13" s="85"/>
-      <c r="E13" s="76"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="68"/>
       <c r="F13" s="9"/>
-      <c r="G13" s="79"/>
+      <c r="G13" s="71"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="79"/>
+      <c r="I13" s="71"/>
       <c r="J13" s="10"/>
       <c r="K13" s="4"/>
       <c r="L13" s="9"/>
       <c r="M13" s="3"/>
-      <c r="N13" s="81"/>
-      <c r="O13" s="81"/>
+      <c r="N13" s="73"/>
+      <c r="O13" s="73"/>
       <c r="P13" s="11"/>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B14" s="61"/>
+      <c r="B14" s="55"/>
       <c r="C14" s="8"/>
-      <c r="D14" s="85"/>
-      <c r="E14" s="76"/>
+      <c r="D14" s="77"/>
+      <c r="E14" s="68"/>
       <c r="F14" s="9"/>
-      <c r="G14" s="79"/>
+      <c r="G14" s="71"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="79"/>
+      <c r="I14" s="71"/>
       <c r="J14" s="10"/>
       <c r="K14" s="4"/>
       <c r="L14" s="9"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="81"/>
-      <c r="O14" s="81"/>
+      <c r="N14" s="73"/>
+      <c r="O14" s="73"/>
       <c r="P14" s="11"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B15" s="61"/>
+      <c r="B15" s="55"/>
       <c r="C15" s="8"/>
-      <c r="D15" s="85"/>
-      <c r="E15" s="76"/>
+      <c r="D15" s="77"/>
+      <c r="E15" s="68"/>
       <c r="F15" s="9"/>
-      <c r="G15" s="79"/>
+      <c r="G15" s="71"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="79"/>
+      <c r="I15" s="71"/>
       <c r="J15" s="10"/>
       <c r="K15" s="4"/>
       <c r="L15" s="9"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="81"/>
-      <c r="O15" s="81"/>
+      <c r="N15" s="73"/>
+      <c r="O15" s="73"/>
       <c r="P15" s="11"/>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B16" s="61"/>
+      <c r="B16" s="55"/>
       <c r="C16" s="8"/>
-      <c r="D16" s="85"/>
-      <c r="E16" s="76"/>
+      <c r="D16" s="77"/>
+      <c r="E16" s="68"/>
       <c r="F16" s="9"/>
-      <c r="G16" s="79"/>
+      <c r="G16" s="71"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="79"/>
+      <c r="I16" s="71"/>
       <c r="J16" s="10"/>
       <c r="K16" s="4"/>
       <c r="L16" s="9"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="81"/>
-      <c r="O16" s="81"/>
+      <c r="N16" s="73"/>
+      <c r="O16" s="73"/>
       <c r="P16" s="11"/>
     </row>
     <row r="17" spans="2:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="63"/>
+      <c r="B17" s="57"/>
       <c r="C17" s="12"/>
-      <c r="D17" s="86"/>
-      <c r="E17" s="77"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="69"/>
       <c r="F17" s="13"/>
-      <c r="G17" s="80"/>
+      <c r="G17" s="72"/>
       <c r="H17" s="13"/>
-      <c r="I17" s="80"/>
+      <c r="I17" s="72"/>
       <c r="J17" s="14"/>
       <c r="K17" s="15"/>
       <c r="L17" s="13"/>
       <c r="M17" s="16"/>
-      <c r="N17" s="82"/>
-      <c r="O17" s="82"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="74"/>
       <c r="P17" s="17"/>
     </row>
   </sheetData>
@@ -4047,59 +4162,59 @@
   <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.5" style="107" customWidth="1"/>
-    <col min="2" max="2" width="17.5" style="108" customWidth="1"/>
+    <col min="1" max="1" width="14.5" style="99" customWidth="1"/>
+    <col min="2" max="2" width="17.5" style="100" customWidth="1"/>
     <col min="3" max="3" width="20.33203125" customWidth="1"/>
     <col min="4" max="4" width="30.5" customWidth="1"/>
-    <col min="5" max="5" width="24.5" style="117" customWidth="1"/>
+    <col min="5" max="5" width="24.5" style="109" customWidth="1"/>
     <col min="6" max="6" width="46.5" customWidth="1"/>
     <col min="7" max="7" width="35.5" customWidth="1"/>
-    <col min="8" max="8" width="25.33203125" style="109" customWidth="1"/>
+    <col min="8" max="8" width="25.33203125" style="101" customWidth="1"/>
     <col min="9" max="9" width="41.5" customWidth="1"/>
-    <col min="10" max="10" width="19.6640625" style="110" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" style="102" customWidth="1"/>
     <col min="11" max="11" width="37.33203125" customWidth="1"/>
     <col min="12" max="12" width="39.1640625" customWidth="1"/>
-    <col min="13" max="13" width="38.5" style="108" customWidth="1"/>
+    <col min="13" max="13" width="38.5" style="100" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="32.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="110" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="118" t="s">
+      <c r="B1" s="110" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="118" t="s">
+      <c r="C1" s="110" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="118" t="s">
+      <c r="D1" s="110" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="118" t="s">
+      <c r="E1" s="110" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="118" t="s">
+      <c r="F1" s="110" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="118" t="s">
+      <c r="G1" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="119" t="s">
+      <c r="H1" s="111" t="s">
         <v>52</v>
       </c>
-      <c r="I1" s="118" t="s">
+      <c r="I1" s="110" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="118" t="s">
+      <c r="J1" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="118" t="s">
+      <c r="K1" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="120" t="s">
+      <c r="L1" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="M1" s="118" t="s">
+      <c r="M1" s="110" t="s">
         <v>53</v>
       </c>
     </row>
@@ -4112,7 +4227,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB86416B-95D3-4BD2-8FFB-7DA9193C6FDC}">
-  <dimension ref="B1:G24"/>
+  <dimension ref="B1:G45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.83203125" customWidth="1"/>
@@ -4125,49 +4240,49 @@
   <sheetData>
     <row r="1" spans="2:7" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:7" ht="26" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="127" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="122"/>
-      <c r="D2" s="122"/>
-      <c r="E2" s="122"/>
-      <c r="F2" s="122"/>
-      <c r="G2" s="123"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="129"/>
     </row>
     <row r="3" spans="2:7" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="140" t="s">
+      <c r="B3" s="133" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="140"/>
-      <c r="D3" s="140"/>
-      <c r="E3" s="140"/>
-      <c r="F3" s="140" t="s">
+      <c r="C3" s="133"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="133"/>
+      <c r="F3" s="133" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="140"/>
-    </row>
-    <row r="4" spans="2:7" ht="56" x14ac:dyDescent="0.2">
-      <c r="B4" s="49" t="s">
+      <c r="G3" s="133"/>
+    </row>
+    <row r="4" spans="2:7" ht="57" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="151" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="50" t="s">
+      <c r="C4" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="50" t="s">
+      <c r="D4" s="113" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="50" t="s">
+      <c r="E4" s="113" t="s">
         <v>56</v>
       </c>
-      <c r="F4" s="50" t="s">
+      <c r="F4" s="113" t="s">
         <v>57</v>
       </c>
-      <c r="G4" s="51" t="s">
+      <c r="G4" s="113" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B5" s="60">
+      <c r="B5" s="54">
         <v>1</v>
       </c>
       <c r="C5" s="18" t="s">
@@ -4176,167 +4291,335 @@
       <c r="D5" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="94" t="s">
+      <c r="E5" s="86" t="s">
         <v>58</v>
       </c>
-      <c r="F5" s="93" t="s">
+      <c r="F5" s="85" t="s">
         <v>58</v>
       </c>
       <c r="G5" s="20"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B6" s="61">
+      <c r="B6" s="55">
         <v>2</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="94"/>
-      <c r="F6" s="65"/>
+      <c r="E6" s="86"/>
+      <c r="F6" s="59"/>
       <c r="G6" s="11"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="61"/>
+      <c r="B7" s="55"/>
       <c r="C7" s="1"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="65"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="59"/>
       <c r="G7" s="11"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B8" s="61"/>
+      <c r="B8" s="55"/>
       <c r="C8" s="1"/>
       <c r="D8" s="3"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="65"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="59"/>
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B9" s="61"/>
+      <c r="B9" s="55"/>
       <c r="C9" s="1"/>
       <c r="D9" s="3"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="65"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="59"/>
       <c r="G9" s="11"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B10" s="61"/>
+      <c r="B10" s="55"/>
       <c r="C10" s="1"/>
       <c r="D10" s="3"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="65"/>
+      <c r="E10" s="58"/>
+      <c r="F10" s="59"/>
       <c r="G10" s="11"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B11" s="61"/>
+      <c r="B11" s="55"/>
       <c r="C11" s="1"/>
       <c r="D11" s="3"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="65"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="59"/>
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B12" s="62"/>
+      <c r="B12" s="56"/>
       <c r="C12" s="1"/>
       <c r="D12" s="3"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="65"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="59"/>
       <c r="G12" s="11"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B13" s="61"/>
+      <c r="B13" s="55"/>
       <c r="C13" s="1"/>
       <c r="D13" s="3"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="65"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="59"/>
       <c r="G13" s="11"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B14" s="61"/>
+      <c r="B14" s="55"/>
       <c r="C14" s="1"/>
       <c r="D14" s="3"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="65"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="59"/>
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="61"/>
+      <c r="B15" s="55"/>
       <c r="C15" s="1"/>
       <c r="D15" s="3"/>
-      <c r="E15" s="64"/>
-      <c r="F15" s="65"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="59"/>
       <c r="G15" s="11"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B16" s="61"/>
+      <c r="B16" s="55"/>
       <c r="C16" s="1"/>
       <c r="D16" s="3"/>
-      <c r="E16" s="64"/>
-      <c r="F16" s="65"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="59"/>
       <c r="G16" s="11"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B17" s="61"/>
+      <c r="B17" s="55"/>
       <c r="C17" s="1"/>
       <c r="D17" s="3"/>
-      <c r="E17" s="64"/>
-      <c r="F17" s="65"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="59"/>
       <c r="G17" s="11"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B18" s="61"/>
+      <c r="B18" s="55"/>
       <c r="C18" s="1"/>
       <c r="D18" s="3"/>
-      <c r="E18" s="64"/>
-      <c r="F18" s="65"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="59"/>
       <c r="G18" s="11"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B19" s="61"/>
+      <c r="B19" s="55"/>
       <c r="C19" s="5"/>
       <c r="D19" s="6"/>
-      <c r="E19" s="64"/>
-      <c r="F19" s="65"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="59"/>
       <c r="G19" s="11"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B20" s="61"/>
+      <c r="B20" s="55"/>
       <c r="C20" s="8"/>
       <c r="D20" s="9"/>
-      <c r="E20" s="64"/>
-      <c r="F20" s="65"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="59"/>
       <c r="G20" s="11"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B21" s="61"/>
+      <c r="B21" s="55"/>
       <c r="C21" s="8"/>
       <c r="D21" s="9"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="65"/>
+      <c r="E21" s="58"/>
+      <c r="F21" s="59"/>
       <c r="G21" s="11"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B22" s="61"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="64"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="11"/>
+      <c r="B22" s="137"/>
+      <c r="C22" s="138"/>
+      <c r="D22" s="139"/>
+      <c r="E22" s="140"/>
+      <c r="F22" s="141"/>
+      <c r="G22" s="142"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B23" s="61"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="64"/>
-      <c r="F23" s="65"/>
+      <c r="B23" s="55"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="59"/>
       <c r="G23" s="11"/>
     </row>
-    <row r="24" spans="2:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="63"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="66"/>
-      <c r="F24" s="67"/>
-      <c r="G24" s="17"/>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B24" s="55"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="11"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B25" s="55"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="58"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="11"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B26" s="55"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="11"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B27" s="55"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="58"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="11"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B28" s="55"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="58"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="11"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B29" s="55"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="58"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="11"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B30" s="55"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="58"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="11"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B31" s="55"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="11"/>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B32" s="55"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="58"/>
+      <c r="F32" s="59"/>
+      <c r="G32" s="11"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B33" s="55"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="58"/>
+      <c r="F33" s="59"/>
+      <c r="G33" s="11"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B34" s="55"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="58"/>
+      <c r="F34" s="59"/>
+      <c r="G34" s="11"/>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B35" s="55"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="11"/>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B36" s="55"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="59"/>
+      <c r="G36" s="11"/>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B37" s="55"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="58"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="11"/>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B38" s="55"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="59"/>
+      <c r="G38" s="11"/>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B39" s="55"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="58"/>
+      <c r="F39" s="59"/>
+      <c r="G39" s="11"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B40" s="55"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="11"/>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B41" s="55"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="58"/>
+      <c r="F41" s="59"/>
+      <c r="G41" s="11"/>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B42" s="55"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="58"/>
+      <c r="F42" s="59"/>
+      <c r="G42" s="11"/>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B43" s="55"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="58"/>
+      <c r="F43" s="59"/>
+      <c r="G43" s="11"/>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B44" s="55"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="58"/>
+      <c r="F44" s="59"/>
+      <c r="G44" s="11"/>
+    </row>
+    <row r="45" spans="2:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="143"/>
+      <c r="C45" s="144"/>
+      <c r="D45" s="145"/>
+      <c r="E45" s="146"/>
+      <c r="F45" s="147"/>
+      <c r="G45" s="148"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4345,7 +4628,7 @@
     <mergeCell ref="F3:G3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C24" xr:uid="{DB3F6F4F-BFDE-478E-B451-3796038FFC34}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C45" xr:uid="{DB3F6F4F-BFDE-478E-B451-3796038FFC34}">
       <formula1>"1st, 2nd, 3rd, 4th, 5th "</formula1>
     </dataValidation>
   </dataValidations>
@@ -4951,99 +5234,99 @@
       <c r="E1" s="22"/>
       <c r="F1" s="22"/>
       <c r="G1" s="22"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
     </row>
     <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="24"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95" t="s">
+      <c r="B2" s="87"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
+      <c r="I2" s="87" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="25"/>
-      <c r="B3" s="95"/>
+      <c r="B3" s="87"/>
       <c r="C3" s="26"/>
-      <c r="D3" s="96"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="95"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
       <c r="I3" s="27"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A4" s="97"/>
-      <c r="B4" s="95"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="87"/>
       <c r="C4" s="26"/>
-      <c r="D4" s="96"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="95"/>
-      <c r="H4" s="95"/>
-      <c r="I4" s="95"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A5" s="98"/>
-      <c r="B5" s="95"/>
+      <c r="A5" s="90"/>
+      <c r="B5" s="87"/>
       <c r="C5" s="26"/>
-      <c r="D5" s="96"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="96"/>
-      <c r="G5" s="95"/>
-      <c r="H5" s="95"/>
-      <c r="I5" s="95"/>
+      <c r="D5" s="88"/>
+      <c r="E5" s="88"/>
+      <c r="F5" s="88"/>
+      <c r="G5" s="87"/>
+      <c r="H5" s="87"/>
+      <c r="I5" s="87"/>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B23" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="95"/>
-      <c r="D23" s="95"/>
-      <c r="E23" s="95"/>
-      <c r="F23" s="95"/>
-      <c r="G23" s="95"/>
-      <c r="H23" s="95"/>
-      <c r="I23" s="95"/>
-      <c r="J23" s="95"/>
-      <c r="K23" s="95"/>
+      <c r="C23" s="87"/>
+      <c r="D23" s="87"/>
+      <c r="E23" s="87"/>
+      <c r="F23" s="87"/>
+      <c r="G23" s="87"/>
+      <c r="H23" s="87"/>
+      <c r="I23" s="87"/>
+      <c r="J23" s="87"/>
+      <c r="K23" s="87"/>
     </row>
     <row r="28" spans="2:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="B28" s="95"/>
-      <c r="C28" s="95"/>
+      <c r="B28" s="87"/>
+      <c r="C28" s="87"/>
       <c r="D28" s="29" t="str">
         <f ca="1">"The first "&amp;COUNT(I33:I47)&amp;" "&amp;C32&amp;" cover "&amp;TEXT(OFFSET(E32,COUNT(I33:I47),0,1,1),"0.??%")&amp;" of the Total "&amp;D32</f>
         <v>The first 3 Causes cover 87.96% of the Total Defects</v>
       </c>
-      <c r="E28" s="95"/>
-      <c r="F28" s="95"/>
-      <c r="G28" s="95"/>
-      <c r="H28" s="95"/>
-      <c r="I28" s="95"/>
-      <c r="J28" s="95"/>
-      <c r="K28" s="95"/>
+      <c r="E28" s="87"/>
+      <c r="F28" s="87"/>
+      <c r="G28" s="87"/>
+      <c r="H28" s="87"/>
+      <c r="I28" s="87"/>
+      <c r="J28" s="87"/>
+      <c r="K28" s="87"/>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B31" s="95"/>
-      <c r="C31" s="95"/>
-      <c r="D31" s="99" t="s">
+      <c r="B31" s="87"/>
+      <c r="C31" s="87"/>
+      <c r="D31" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="E31" s="100">
+      <c r="E31" s="92">
         <v>0.8</v>
       </c>
-      <c r="F31" s="95"/>
-      <c r="G31" s="95"/>
-      <c r="H31" s="95"/>
-      <c r="I31" s="95"/>
-      <c r="J31" s="95"/>
-      <c r="K31" s="95"/>
+      <c r="F31" s="87"/>
+      <c r="G31" s="87"/>
+      <c r="H31" s="87"/>
+      <c r="I31" s="87"/>
+      <c r="J31" s="87"/>
+      <c r="K31" s="87"/>
     </row>
     <row r="32" spans="2:11" ht="16" x14ac:dyDescent="0.2">
       <c r="B32" s="30" t="s">
@@ -5058,9 +5341,9 @@
       <c r="E32" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="F32" s="95"/>
-      <c r="G32" s="95"/>
-      <c r="H32" s="95"/>
+      <c r="F32" s="87"/>
+      <c r="G32" s="87"/>
+      <c r="H32" s="87"/>
       <c r="I32" s="33" t="s">
         <v>66</v>
       </c>
@@ -5072,23 +5355,23 @@
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B33" s="101">
+      <c r="B33" s="93">
         <f t="shared" ref="B33:B47" si="0">ROW(B33)-ROW($B$32)</f>
         <v>1</v>
       </c>
-      <c r="C33" s="102" t="s">
+      <c r="C33" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="D33" s="103">
+      <c r="D33" s="95">
         <v>50</v>
       </c>
-      <c r="E33" s="104">
+      <c r="E33" s="96">
         <f>SUM(D33:D$33)/SUM($D$33:$D$47)</f>
         <v>0.46296296296296297</v>
       </c>
-      <c r="F33" s="95"/>
-      <c r="G33" s="95"/>
-      <c r="H33" s="95"/>
+      <c r="F33" s="87"/>
+      <c r="G33" s="87"/>
+      <c r="H33" s="87"/>
       <c r="I33" s="34">
         <f t="shared" ref="I33:I47" ca="1" si="1">IF(OR(B33=1,OFFSET($E$32,B33-1,0,1,1)&lt;=$E$31),OFFSET($D$32,B33,0,1,1),"")</f>
         <v>50</v>
@@ -5103,23 +5386,23 @@
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B34" s="101">
+      <c r="B34" s="93">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C34" s="102" t="s">
+      <c r="C34" s="94" t="s">
         <v>70</v>
       </c>
-      <c r="D34" s="103">
+      <c r="D34" s="95">
         <v>30</v>
       </c>
-      <c r="E34" s="104">
+      <c r="E34" s="96">
         <f>SUM(D$33:D34)/SUM($D$33:$D$47)</f>
         <v>0.7407407407407407</v>
       </c>
-      <c r="F34" s="95"/>
-      <c r="G34" s="95"/>
-      <c r="H34" s="95"/>
+      <c r="F34" s="87"/>
+      <c r="G34" s="87"/>
+      <c r="H34" s="87"/>
       <c r="I34" s="34">
         <f t="shared" ca="1" si="1"/>
         <v>30</v>
@@ -5134,23 +5417,23 @@
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B35" s="101">
+      <c r="B35" s="93">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C35" s="102" t="s">
+      <c r="C35" s="94" t="s">
         <v>71</v>
       </c>
-      <c r="D35" s="103">
+      <c r="D35" s="95">
         <v>15</v>
       </c>
-      <c r="E35" s="104">
+      <c r="E35" s="96">
         <f>SUM(D$33:D35)/SUM($D$33:$D$47)</f>
         <v>0.87962962962962965</v>
       </c>
-      <c r="F35" s="95"/>
-      <c r="G35" s="95"/>
-      <c r="H35" s="95"/>
+      <c r="F35" s="87"/>
+      <c r="G35" s="87"/>
+      <c r="H35" s="87"/>
       <c r="I35" s="34">
         <f t="shared" ca="1" si="1"/>
         <v>15</v>
@@ -5165,23 +5448,23 @@
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B36" s="101">
+      <c r="B36" s="93">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C36" s="102" t="s">
+      <c r="C36" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D36" s="103">
+      <c r="D36" s="95">
         <v>5</v>
       </c>
-      <c r="E36" s="104">
+      <c r="E36" s="96">
         <f>SUM(D$33:D36)/SUM($D$33:$D$47)</f>
         <v>0.92592592592592593</v>
       </c>
-      <c r="F36" s="95"/>
-      <c r="G36" s="95"/>
-      <c r="H36" s="95"/>
+      <c r="F36" s="87"/>
+      <c r="G36" s="87"/>
+      <c r="H36" s="87"/>
       <c r="I36" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -5196,23 +5479,23 @@
       </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B37" s="101">
+      <c r="B37" s="93">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C37" s="102" t="s">
+      <c r="C37" s="94" t="s">
         <v>73</v>
       </c>
-      <c r="D37" s="103">
+      <c r="D37" s="95">
         <v>3</v>
       </c>
-      <c r="E37" s="104">
+      <c r="E37" s="96">
         <f>SUM(D$33:D37)/SUM($D$33:$D$47)</f>
         <v>0.95370370370370372</v>
       </c>
-      <c r="F37" s="95"/>
-      <c r="G37" s="95"/>
-      <c r="H37" s="95"/>
+      <c r="F37" s="87"/>
+      <c r="G37" s="87"/>
+      <c r="H37" s="87"/>
       <c r="I37" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -5227,23 +5510,23 @@
       </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B38" s="101">
+      <c r="B38" s="93">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C38" s="102" t="s">
+      <c r="C38" s="94" t="s">
         <v>74</v>
       </c>
-      <c r="D38" s="103">
+      <c r="D38" s="95">
         <v>2</v>
       </c>
-      <c r="E38" s="104">
+      <c r="E38" s="96">
         <f>SUM(D$33:D38)/SUM($D$33:$D$47)</f>
         <v>0.97222222222222221</v>
       </c>
-      <c r="F38" s="95"/>
-      <c r="G38" s="95"/>
-      <c r="H38" s="95"/>
+      <c r="F38" s="87"/>
+      <c r="G38" s="87"/>
+      <c r="H38" s="87"/>
       <c r="I38" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -5258,23 +5541,23 @@
       </c>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B39" s="101">
+      <c r="B39" s="93">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C39" s="102" t="s">
+      <c r="C39" s="94" t="s">
         <v>75</v>
       </c>
-      <c r="D39" s="103">
+      <c r="D39" s="95">
         <v>1</v>
       </c>
-      <c r="E39" s="104">
+      <c r="E39" s="96">
         <f>SUM(D$33:D39)/SUM($D$33:$D$47)</f>
         <v>0.98148148148148151</v>
       </c>
-      <c r="F39" s="95"/>
-      <c r="G39" s="95"/>
-      <c r="H39" s="95"/>
+      <c r="F39" s="87"/>
+      <c r="G39" s="87"/>
+      <c r="H39" s="87"/>
       <c r="I39" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -5289,23 +5572,23 @@
       </c>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B40" s="101">
+      <c r="B40" s="93">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C40" s="102" t="s">
+      <c r="C40" s="94" t="s">
         <v>76</v>
       </c>
-      <c r="D40" s="103">
+      <c r="D40" s="95">
         <v>1</v>
       </c>
-      <c r="E40" s="104">
+      <c r="E40" s="96">
         <f>SUM(D$33:D40)/SUM($D$33:$D$47)</f>
         <v>0.9907407407407407</v>
       </c>
-      <c r="F40" s="95"/>
-      <c r="G40" s="95"/>
-      <c r="H40" s="95"/>
+      <c r="F40" s="87"/>
+      <c r="G40" s="87"/>
+      <c r="H40" s="87"/>
       <c r="I40" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -5320,23 +5603,23 @@
       </c>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B41" s="101">
+      <c r="B41" s="93">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C41" s="102" t="s">
+      <c r="C41" s="94" t="s">
         <v>77</v>
       </c>
-      <c r="D41" s="103">
+      <c r="D41" s="95">
         <v>1</v>
       </c>
-      <c r="E41" s="104">
+      <c r="E41" s="96">
         <f>SUM(D$33:D41)/SUM($D$33:$D$47)</f>
         <v>1</v>
       </c>
-      <c r="F41" s="95"/>
-      <c r="G41" s="95"/>
-      <c r="H41" s="95"/>
+      <c r="F41" s="87"/>
+      <c r="G41" s="87"/>
+      <c r="H41" s="87"/>
       <c r="I41" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -5351,19 +5634,19 @@
       </c>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B42" s="101">
+      <c r="B42" s="93">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C42" s="102"/>
-      <c r="D42" s="103"/>
-      <c r="E42" s="104">
+      <c r="C42" s="94"/>
+      <c r="D42" s="95"/>
+      <c r="E42" s="96">
         <f>SUM(D$33:D42)/SUM($D$33:$D$47)</f>
         <v>1</v>
       </c>
-      <c r="F42" s="95"/>
-      <c r="G42" s="95"/>
-      <c r="H42" s="95"/>
+      <c r="F42" s="87"/>
+      <c r="G42" s="87"/>
+      <c r="H42" s="87"/>
       <c r="I42" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -5378,19 +5661,19 @@
       </c>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B43" s="101">
+      <c r="B43" s="93">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C43" s="102"/>
-      <c r="D43" s="103"/>
-      <c r="E43" s="104">
+      <c r="C43" s="94"/>
+      <c r="D43" s="95"/>
+      <c r="E43" s="96">
         <f>SUM(D$33:D43)/SUM($D$33:$D$47)</f>
         <v>1</v>
       </c>
-      <c r="F43" s="95"/>
-      <c r="G43" s="95"/>
-      <c r="H43" s="95"/>
+      <c r="F43" s="87"/>
+      <c r="G43" s="87"/>
+      <c r="H43" s="87"/>
       <c r="I43" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -5405,19 +5688,19 @@
       </c>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B44" s="101">
+      <c r="B44" s="93">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C44" s="102"/>
-      <c r="D44" s="103"/>
-      <c r="E44" s="104">
+      <c r="C44" s="94"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="96">
         <f>SUM(D$33:D44)/SUM($D$33:$D$47)</f>
         <v>1</v>
       </c>
-      <c r="F44" s="95"/>
-      <c r="G44" s="95"/>
-      <c r="H44" s="95"/>
+      <c r="F44" s="87"/>
+      <c r="G44" s="87"/>
+      <c r="H44" s="87"/>
       <c r="I44" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -5432,19 +5715,19 @@
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B45" s="101">
+      <c r="B45" s="93">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C45" s="102"/>
-      <c r="D45" s="103"/>
-      <c r="E45" s="104">
+      <c r="C45" s="94"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="96">
         <f>SUM(D$33:D45)/SUM($D$33:$D$47)</f>
         <v>1</v>
       </c>
-      <c r="F45" s="95"/>
-      <c r="G45" s="95"/>
-      <c r="H45" s="95"/>
+      <c r="F45" s="87"/>
+      <c r="G45" s="87"/>
+      <c r="H45" s="87"/>
       <c r="I45" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -5459,19 +5742,19 @@
       </c>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B46" s="101">
+      <c r="B46" s="93">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C46" s="102"/>
-      <c r="D46" s="103"/>
-      <c r="E46" s="104">
+      <c r="C46" s="94"/>
+      <c r="D46" s="95"/>
+      <c r="E46" s="96">
         <f>SUM(D$33:D46)/SUM($D$33:$D$47)</f>
         <v>1</v>
       </c>
-      <c r="F46" s="95"/>
-      <c r="G46" s="95"/>
-      <c r="H46" s="95"/>
+      <c r="F46" s="87"/>
+      <c r="G46" s="87"/>
+      <c r="H46" s="87"/>
       <c r="I46" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -5486,19 +5769,19 @@
       </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B47" s="101">
+      <c r="B47" s="93">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C47" s="102"/>
-      <c r="D47" s="103"/>
-      <c r="E47" s="104">
+      <c r="C47" s="94"/>
+      <c r="D47" s="95"/>
+      <c r="E47" s="96">
         <f>SUM(D$33:D47)/SUM($D$33:$D$47)</f>
         <v>1</v>
       </c>
-      <c r="F47" s="95"/>
-      <c r="G47" s="95"/>
-      <c r="H47" s="95"/>
+      <c r="F47" s="87"/>
+      <c r="G47" s="87"/>
+      <c r="H47" s="87"/>
       <c r="I47" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
@@ -5519,9 +5802,9 @@
       <c r="C48" s="22"/>
       <c r="D48" s="22"/>
       <c r="E48" s="22"/>
-      <c r="F48" s="95"/>
-      <c r="G48" s="95"/>
-      <c r="H48" s="95"/>
+      <c r="F48" s="87"/>
+      <c r="G48" s="87"/>
+      <c r="H48" s="87"/>
       <c r="I48" s="22"/>
       <c r="J48" s="22"/>
       <c r="K48" s="22"/>
@@ -5540,7 +5823,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45681BFF-6C88-41B3-ABFD-111550758599}">
-  <dimension ref="B1:G11"/>
+  <dimension ref="B1:G44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5" style="40" customWidth="1"/>
@@ -5554,98 +5837,362 @@
   <sheetData>
     <row r="1" spans="2:7" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:7" ht="19" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="141" t="s">
+      <c r="B2" s="134" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
-      <c r="E2" s="142"/>
-      <c r="F2" s="142"/>
-      <c r="G2" s="143"/>
-    </row>
-    <row r="3" spans="2:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="B3" s="52" t="s">
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
+      <c r="E2" s="135"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="136"/>
+    </row>
+    <row r="3" spans="2:7" ht="29" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="149" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" s="150" t="s">
         <v>80</v>
       </c>
-      <c r="D3" s="53" t="s">
+      <c r="D3" s="150" t="s">
         <v>81</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="E3" s="150" t="s">
         <v>82</v>
       </c>
-      <c r="F3" s="53" t="s">
+      <c r="F3" s="150" t="s">
         <v>83</v>
       </c>
-      <c r="G3" s="54" t="s">
+      <c r="G3" s="150" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="68"/>
+      <c r="B4" s="60"/>
       <c r="C4" s="38"/>
       <c r="D4" s="38"/>
       <c r="E4" s="38"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="88"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="80"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B5" s="69"/>
+      <c r="B5" s="61"/>
       <c r="C5" s="39"/>
       <c r="D5" s="39"/>
       <c r="E5" s="39"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="90"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="82"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B6" s="69"/>
+      <c r="B6" s="61"/>
       <c r="C6" s="39"/>
       <c r="D6" s="39"/>
       <c r="E6" s="39"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="90"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="82"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="69"/>
+      <c r="B7" s="61"/>
       <c r="C7" s="39"/>
       <c r="D7" s="39"/>
       <c r="E7" s="39"/>
-      <c r="F7" s="89"/>
-      <c r="G7" s="90"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="82"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B8" s="69"/>
+      <c r="B8" s="61"/>
       <c r="C8" s="39"/>
       <c r="D8" s="39"/>
       <c r="E8" s="39"/>
-      <c r="F8" s="89"/>
-      <c r="G8" s="90"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="82"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B9" s="69"/>
+      <c r="B9" s="61"/>
       <c r="C9" s="39"/>
       <c r="D9" s="39"/>
       <c r="E9" s="39"/>
-      <c r="F9" s="89"/>
-      <c r="G9" s="90"/>
+      <c r="F9" s="81"/>
+      <c r="G9" s="82"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B10" s="69"/>
+      <c r="B10" s="61"/>
       <c r="C10" s="39"/>
       <c r="D10" s="39"/>
       <c r="E10" s="39"/>
-      <c r="F10" s="89"/>
-      <c r="G10" s="90"/>
-    </row>
-    <row r="11" spans="2:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="70"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="55"/>
-      <c r="F11" s="91"/>
-      <c r="G11" s="92"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="82"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B11" s="60"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="79"/>
+      <c r="G11" s="80"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B12" s="61"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="82"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B13" s="61"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="81"/>
+      <c r="G13" s="82"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B14" s="61"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="81"/>
+      <c r="G14" s="82"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B15" s="61"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="81"/>
+      <c r="G15" s="82"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B16" s="61"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="81"/>
+      <c r="G16" s="82"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B17" s="61"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="81"/>
+      <c r="G17" s="82"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B18" s="60"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="79"/>
+      <c r="G18" s="80"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B19" s="61"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="81"/>
+      <c r="G19" s="82"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B20" s="61"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="81"/>
+      <c r="G20" s="82"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B21" s="61"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="81"/>
+      <c r="G21" s="82"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B22" s="61"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="81"/>
+      <c r="G22" s="82"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B23" s="61"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="81"/>
+      <c r="G23" s="82"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B24" s="61"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="81"/>
+      <c r="G24" s="82"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B25" s="60"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="79"/>
+      <c r="G25" s="80"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B26" s="61"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="81"/>
+      <c r="G26" s="82"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B27" s="61"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="81"/>
+      <c r="G27" s="82"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B28" s="61"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="81"/>
+      <c r="G28" s="82"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B29" s="61"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="81"/>
+      <c r="G29" s="82"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B30" s="61"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="81"/>
+      <c r="G30" s="82"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B31" s="61"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="81"/>
+      <c r="G31" s="82"/>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B32" s="60"/>
+      <c r="C32" s="38"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="79"/>
+      <c r="G32" s="80"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B33" s="61"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="82"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B34" s="61"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="81"/>
+      <c r="G34" s="82"/>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B35" s="61"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="81"/>
+      <c r="G35" s="82"/>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B36" s="61"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="81"/>
+      <c r="G36" s="82"/>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B37" s="61"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="81"/>
+      <c r="G37" s="82"/>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B38" s="61"/>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="81"/>
+      <c r="G38" s="82"/>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B39" s="60"/>
+      <c r="C39" s="38"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="79"/>
+      <c r="G39" s="80"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B40" s="61"/>
+      <c r="C40" s="39"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="39"/>
+      <c r="F40" s="81"/>
+      <c r="G40" s="82"/>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B41" s="61"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="81"/>
+      <c r="G41" s="82"/>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B42" s="61"/>
+      <c r="C42" s="39"/>
+      <c r="D42" s="39"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="81"/>
+      <c r="G42" s="82"/>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B43" s="61"/>
+      <c r="C43" s="39"/>
+      <c r="D43" s="39"/>
+      <c r="E43" s="39"/>
+      <c r="F43" s="81"/>
+      <c r="G43" s="82"/>
+    </row>
+    <row r="44" spans="2:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="62"/>
+      <c r="C44" s="49"/>
+      <c r="D44" s="49"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="83"/>
+      <c r="G44" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5656,33 +6203,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="14bdffc1-a38a-4965-b8c7-6b995394fa38">
-      <UserInfo>
-        <DisplayName>WAN HALIMATON SAADIAH BINTI WAN ISMAIL</DisplayName>
-        <AccountId>65</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fa6523cc-f9d2-4d22-b899-9712b14156b8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="14bdffc1-a38a-4965-b8c7-6b995394fa38" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D5AB0CD1DD65FF45ACCBA0C60D1867E8" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9b8b9fc55244cc43035c853b0fde500e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fa6523cc-f9d2-4d22-b899-9712b14156b8" xmlns:ns3="14bdffc1-a38a-4965-b8c7-6b995394fa38" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="965d4105b9913476a602caf9f8528410" ns2:_="" ns3:_="">
     <xsd:import namespace="fa6523cc-f9d2-4d22-b899-9712b14156b8"/>
@@ -5931,10 +6451,48 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="14bdffc1-a38a-4965-b8c7-6b995394fa38">
+      <UserInfo>
+        <DisplayName>WAN HALIMATON SAADIAH BINTI WAN ISMAIL</DisplayName>
+        <AccountId>65</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fa6523cc-f9d2-4d22-b899-9712b14156b8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="14bdffc1-a38a-4965-b8c7-6b995394fa38" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{887577A6-6A39-4FD8-B789-F26250D68B34}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D67D0D37-95F9-4E9C-81FC-9A68C94FD78A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="fa6523cc-f9d2-4d22-b899-9712b14156b8"/>
+    <ds:schemaRef ds:uri="14bdffc1-a38a-4965-b8c7-6b995394fa38"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5951,20 +6509,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D67D0D37-95F9-4E9C-81FC-9A68C94FD78A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{887577A6-6A39-4FD8-B789-F26250D68B34}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="fa6523cc-f9d2-4d22-b899-9712b14156b8"/>
-    <ds:schemaRef ds:uri="14bdffc1-a38a-4965-b8c7-6b995394fa38"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/artifacts/api-server/assets/test-case-template.xlsx
+++ b/artifacts/api-server/assets/test-case-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/syamilabdulsamat/Desktop/QAPulse/QAPulse/artifacts/api-server/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78030303-D649-014D-9A5C-8609B68F7EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B63A017-5137-5F46-95FC-2D36C247A9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4420" yWindow="880" windowWidth="31580" windowHeight="21120" tabRatio="713" activeTab="3" xr2:uid="{01A690A9-14C5-40FC-A7C5-3CCF81F623E0}"/>
+    <workbookView xWindow="4420" yWindow="880" windowWidth="31580" windowHeight="21120" tabRatio="713" xr2:uid="{01A690A9-14C5-40FC-A7C5-3CCF81F623E0}"/>
   </bookViews>
   <sheets>
     <sheet name="Doc Info" sheetId="5" r:id="rId1"/>
@@ -1783,6 +1783,75 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1814,15 +1883,6 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="38" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1832,9 +1892,6 @@
     <xf numFmtId="0" fontId="20" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1843,63 +1900,6 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -3601,7 +3601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D27E4C-6B7C-431B-AD01-A9F1CD922E08}">
-  <dimension ref="B1:G13"/>
+  <dimension ref="B1:G48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
@@ -3614,14 +3614,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="118" t="s">
+      <c r="B1" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="121"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="140"/>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B2" s="41"/>
@@ -3629,17 +3629,17 @@
       <c r="D2" s="98"/>
       <c r="E2" s="41"/>
       <c r="F2" s="41"/>
-      <c r="G2" s="122"/>
+      <c r="G2" s="141"/>
     </row>
     <row r="3" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="118" t="s">
+      <c r="B3" s="137" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="120"/>
-      <c r="G3" s="122"/>
+      <c r="C3" s="138"/>
+      <c r="D3" s="138"/>
+      <c r="E3" s="138"/>
+      <c r="F3" s="139"/>
+      <c r="G3" s="141"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="41"/>
@@ -3652,10 +3652,10 @@
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B5" s="123" t="s">
+      <c r="B5" s="142" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="124"/>
+      <c r="C5" s="143"/>
       <c r="D5" s="103" t="s">
         <v>4</v>
       </c>
@@ -3666,20 +3666,20 @@
     <row r="6" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B6" s="41"/>
       <c r="C6" s="41"/>
-      <c r="D6" s="125"/>
-      <c r="E6" s="125"/>
-      <c r="F6" s="126"/>
+      <c r="D6" s="144"/>
+      <c r="E6" s="144"/>
+      <c r="F6" s="145"/>
       <c r="G6" s="107"/>
     </row>
     <row r="7" spans="2:7" ht="18" x14ac:dyDescent="0.2">
-      <c r="B7" s="114" t="s">
+      <c r="B7" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="115"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="117"/>
+      <c r="C7" s="134"/>
+      <c r="D7" s="135"/>
+      <c r="E7" s="135"/>
+      <c r="F7" s="135"/>
+      <c r="G7" s="136"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="43" t="s">
@@ -3760,6 +3760,356 @@
       <c r="E13" s="42"/>
       <c r="F13" s="42"/>
       <c r="G13" s="64"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B14" s="50">
+        <v>6</v>
+      </c>
+      <c r="C14" s="63"/>
+      <c r="D14" s="97"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="63"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B15" s="51">
+        <v>7</v>
+      </c>
+      <c r="C15" s="64"/>
+      <c r="D15" s="97"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="64"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B16" s="52">
+        <v>8</v>
+      </c>
+      <c r="C16" s="64"/>
+      <c r="D16" s="97"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="65"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B17" s="53">
+        <v>9</v>
+      </c>
+      <c r="C17" s="64"/>
+      <c r="D17" s="97"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="64"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B18" s="53">
+        <v>10</v>
+      </c>
+      <c r="C18" s="64"/>
+      <c r="D18" s="97"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="64"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B19" s="50">
+        <v>11</v>
+      </c>
+      <c r="C19" s="63"/>
+      <c r="D19" s="97"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="63"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B20" s="51">
+        <v>12</v>
+      </c>
+      <c r="C20" s="64"/>
+      <c r="D20" s="97"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="64"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B21" s="52">
+        <v>13</v>
+      </c>
+      <c r="C21" s="64"/>
+      <c r="D21" s="97"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="65"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B22" s="53">
+        <v>14</v>
+      </c>
+      <c r="C22" s="64"/>
+      <c r="D22" s="97"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="64"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B23" s="53">
+        <v>15</v>
+      </c>
+      <c r="C23" s="64"/>
+      <c r="D23" s="97"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="64"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B24" s="50">
+        <v>16</v>
+      </c>
+      <c r="C24" s="63"/>
+      <c r="D24" s="97"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="63"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B25" s="51">
+        <v>17</v>
+      </c>
+      <c r="C25" s="64"/>
+      <c r="D25" s="97"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="64"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B26" s="52">
+        <v>18</v>
+      </c>
+      <c r="C26" s="64"/>
+      <c r="D26" s="97"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="65"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B27" s="53">
+        <v>19</v>
+      </c>
+      <c r="C27" s="64"/>
+      <c r="D27" s="97"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="64"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B28" s="53">
+        <v>20</v>
+      </c>
+      <c r="C28" s="64"/>
+      <c r="D28" s="97"/>
+      <c r="E28" s="42"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="64"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B29" s="50">
+        <v>21</v>
+      </c>
+      <c r="C29" s="63"/>
+      <c r="D29" s="97"/>
+      <c r="E29" s="42"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="63"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B30" s="51">
+        <v>22</v>
+      </c>
+      <c r="C30" s="64"/>
+      <c r="D30" s="97"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="64"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B31" s="52">
+        <v>23</v>
+      </c>
+      <c r="C31" s="64"/>
+      <c r="D31" s="97"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="42"/>
+      <c r="G31" s="65"/>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B32" s="53">
+        <v>24</v>
+      </c>
+      <c r="C32" s="64"/>
+      <c r="D32" s="97"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="64"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B33" s="53">
+        <v>25</v>
+      </c>
+      <c r="C33" s="64"/>
+      <c r="D33" s="97"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="64"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B34" s="50">
+        <v>26</v>
+      </c>
+      <c r="C34" s="63"/>
+      <c r="D34" s="97"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="63"/>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B35" s="51">
+        <v>27</v>
+      </c>
+      <c r="C35" s="64"/>
+      <c r="D35" s="97"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="64"/>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B36" s="52">
+        <v>28</v>
+      </c>
+      <c r="C36" s="64"/>
+      <c r="D36" s="97"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="65"/>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B37" s="53">
+        <v>29</v>
+      </c>
+      <c r="C37" s="64"/>
+      <c r="D37" s="97"/>
+      <c r="E37" s="42"/>
+      <c r="F37" s="42"/>
+      <c r="G37" s="64"/>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B38" s="53">
+        <v>30</v>
+      </c>
+      <c r="C38" s="64"/>
+      <c r="D38" s="97"/>
+      <c r="E38" s="42"/>
+      <c r="F38" s="42"/>
+      <c r="G38" s="64"/>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B39" s="50">
+        <v>31</v>
+      </c>
+      <c r="C39" s="63"/>
+      <c r="D39" s="97"/>
+      <c r="E39" s="42"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="63"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B40" s="51">
+        <v>32</v>
+      </c>
+      <c r="C40" s="64"/>
+      <c r="D40" s="97"/>
+      <c r="E40" s="42"/>
+      <c r="F40" s="42"/>
+      <c r="G40" s="64"/>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B41" s="52">
+        <v>33</v>
+      </c>
+      <c r="C41" s="64"/>
+      <c r="D41" s="97"/>
+      <c r="E41" s="42"/>
+      <c r="F41" s="42"/>
+      <c r="G41" s="65"/>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B42" s="53">
+        <v>34</v>
+      </c>
+      <c r="C42" s="64"/>
+      <c r="D42" s="97"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="64"/>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B43" s="53">
+        <v>35</v>
+      </c>
+      <c r="C43" s="64"/>
+      <c r="D43" s="97"/>
+      <c r="E43" s="42"/>
+      <c r="F43" s="42"/>
+      <c r="G43" s="64"/>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B44" s="50">
+        <v>36</v>
+      </c>
+      <c r="C44" s="63"/>
+      <c r="D44" s="97"/>
+      <c r="E44" s="42"/>
+      <c r="F44" s="42"/>
+      <c r="G44" s="63"/>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B45" s="51">
+        <v>37</v>
+      </c>
+      <c r="C45" s="64"/>
+      <c r="D45" s="97"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="64"/>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B46" s="52">
+        <v>38</v>
+      </c>
+      <c r="C46" s="64"/>
+      <c r="D46" s="97"/>
+      <c r="E46" s="42"/>
+      <c r="F46" s="42"/>
+      <c r="G46" s="65"/>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B47" s="53">
+        <v>39</v>
+      </c>
+      <c r="C47" s="64"/>
+      <c r="D47" s="97"/>
+      <c r="E47" s="42"/>
+      <c r="F47" s="42"/>
+      <c r="G47" s="64"/>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B48" s="53">
+        <v>40</v>
+      </c>
+      <c r="C48" s="64"/>
+      <c r="D48" s="97"/>
+      <c r="E48" s="42"/>
+      <c r="F48" s="42"/>
+      <c r="G48" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -3797,44 +4147,44 @@
   <sheetData>
     <row r="1" spans="2:16" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:16" ht="26" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="129" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="128"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="128"/>
-      <c r="J2" s="128"/>
-      <c r="K2" s="128"/>
-      <c r="L2" s="128"/>
-      <c r="M2" s="128"/>
-      <c r="N2" s="128"/>
-      <c r="O2" s="128"/>
-      <c r="P2" s="129"/>
+      <c r="C2" s="130"/>
+      <c r="D2" s="130"/>
+      <c r="E2" s="130"/>
+      <c r="F2" s="130"/>
+      <c r="G2" s="130"/>
+      <c r="H2" s="130"/>
+      <c r="I2" s="130"/>
+      <c r="J2" s="130"/>
+      <c r="K2" s="130"/>
+      <c r="L2" s="130"/>
+      <c r="M2" s="130"/>
+      <c r="N2" s="130"/>
+      <c r="O2" s="130"/>
+      <c r="P2" s="131"/>
     </row>
     <row r="3" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="130" t="s">
+      <c r="B3" s="146" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="131"/>
-      <c r="D3" s="131"/>
-      <c r="E3" s="131"/>
-      <c r="F3" s="131"/>
-      <c r="G3" s="131"/>
-      <c r="H3" s="131"/>
-      <c r="I3" s="131"/>
-      <c r="J3" s="131"/>
-      <c r="K3" s="131"/>
+      <c r="C3" s="147"/>
+      <c r="D3" s="147"/>
+      <c r="E3" s="147"/>
+      <c r="F3" s="147"/>
+      <c r="G3" s="147"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="147"/>
+      <c r="J3" s="147"/>
+      <c r="K3" s="147"/>
       <c r="L3" s="45"/>
-      <c r="M3" s="131" t="s">
+      <c r="M3" s="147" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="131"/>
-      <c r="O3" s="131"/>
-      <c r="P3" s="132"/>
+      <c r="N3" s="147"/>
+      <c r="O3" s="147"/>
+      <c r="P3" s="148"/>
     </row>
     <row r="4" spans="2:16" ht="71" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="46" t="s">
@@ -4240,29 +4590,29 @@
   <sheetData>
     <row r="1" spans="2:7" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:7" ht="26" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="129" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="129"/>
+      <c r="C2" s="130"/>
+      <c r="D2" s="130"/>
+      <c r="E2" s="130"/>
+      <c r="F2" s="130"/>
+      <c r="G2" s="131"/>
     </row>
     <row r="3" spans="2:7" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="133" t="s">
+      <c r="B3" s="132" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="133"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="133"/>
-      <c r="F3" s="133" t="s">
+      <c r="C3" s="132"/>
+      <c r="D3" s="132"/>
+      <c r="E3" s="132"/>
+      <c r="F3" s="132" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="133"/>
+      <c r="G3" s="132"/>
     </row>
     <row r="4" spans="2:7" ht="57" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="151" t="s">
+      <c r="B4" s="128" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="113" t="s">
@@ -4430,12 +4780,12 @@
       <c r="G21" s="11"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B22" s="137"/>
-      <c r="C22" s="138"/>
-      <c r="D22" s="139"/>
-      <c r="E22" s="140"/>
-      <c r="F22" s="141"/>
-      <c r="G22" s="142"/>
+      <c r="B22" s="114"/>
+      <c r="C22" s="115"/>
+      <c r="D22" s="116"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="118"/>
+      <c r="G22" s="119"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="55"/>
@@ -4614,12 +4964,12 @@
       <c r="G44" s="11"/>
     </row>
     <row r="45" spans="2:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="143"/>
-      <c r="C45" s="144"/>
-      <c r="D45" s="145"/>
-      <c r="E45" s="146"/>
-      <c r="F45" s="147"/>
-      <c r="G45" s="148"/>
+      <c r="B45" s="120"/>
+      <c r="C45" s="121"/>
+      <c r="D45" s="122"/>
+      <c r="E45" s="123"/>
+      <c r="F45" s="124"/>
+      <c r="G45" s="125"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5837,32 +6187,32 @@
   <sheetData>
     <row r="1" spans="2:7" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:7" ht="19" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="134" t="s">
+      <c r="B2" s="149" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="136"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="150"/>
+      <c r="G2" s="151"/>
     </row>
     <row r="3" spans="2:7" ht="29" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="149" t="s">
+      <c r="B3" s="126" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="150" t="s">
+      <c r="C3" s="127" t="s">
         <v>80</v>
       </c>
-      <c r="D3" s="150" t="s">
+      <c r="D3" s="127" t="s">
         <v>81</v>
       </c>
-      <c r="E3" s="150" t="s">
+      <c r="E3" s="127" t="s">
         <v>82</v>
       </c>
-      <c r="F3" s="150" t="s">
+      <c r="F3" s="127" t="s">
         <v>83</v>
       </c>
-      <c r="G3" s="150" t="s">
+      <c r="G3" s="127" t="s">
         <v>84</v>
       </c>
     </row>
@@ -6203,6 +6553,33 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="14bdffc1-a38a-4965-b8c7-6b995394fa38">
+      <UserInfo>
+        <DisplayName>WAN HALIMATON SAADIAH BINTI WAN ISMAIL</DisplayName>
+        <AccountId>65</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fa6523cc-f9d2-4d22-b899-9712b14156b8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="14bdffc1-a38a-4965-b8c7-6b995394fa38" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D5AB0CD1DD65FF45ACCBA0C60D1867E8" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9b8b9fc55244cc43035c853b0fde500e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fa6523cc-f9d2-4d22-b899-9712b14156b8" xmlns:ns3="14bdffc1-a38a-4965-b8c7-6b995394fa38" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="965d4105b9913476a602caf9f8528410" ns2:_="" ns3:_="">
     <xsd:import namespace="fa6523cc-f9d2-4d22-b899-9712b14156b8"/>
@@ -6451,34 +6828,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="14bdffc1-a38a-4965-b8c7-6b995394fa38">
-      <UserInfo>
-        <DisplayName>WAN HALIMATON SAADIAH BINTI WAN ISMAIL</DisplayName>
-        <AccountId>65</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fa6523cc-f9d2-4d22-b899-9712b14156b8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="14bdffc1-a38a-4965-b8c7-6b995394fa38" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{887577A6-6A39-4FD8-B789-F26250D68B34}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C751A3DA-DA6E-456D-B998-BFDFBC6A10B1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="14bdffc1-a38a-4965-b8c7-6b995394fa38"/>
+    <ds:schemaRef ds:uri="fa6523cc-f9d2-4d22-b899-9712b14156b8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D67D0D37-95F9-4E9C-81FC-9A68C94FD78A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6495,23 +6864,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C751A3DA-DA6E-456D-B998-BFDFBC6A10B1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="14bdffc1-a38a-4965-b8c7-6b995394fa38"/>
-    <ds:schemaRef ds:uri="fa6523cc-f9d2-4d22-b899-9712b14156b8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{887577A6-6A39-4FD8-B789-F26250D68B34}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>